--- a/01_analyses_states/Odisha/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Odisha/results/SoIB_summaries.xlsx
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -584,10 +584,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C8">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +682,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -690,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -698,7 +698,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -746,7 +746,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -792,16 +792,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>81.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -812,13 +812,13 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="D3">
         <v>18</v>
       </c>
       <c r="E3">
-        <v>18.2</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
